--- a/forms/trg/Formulir_TRG_cpcd.xlsx
+++ b/forms/trg/Formulir_TRG_cpcd.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B35)</f>
+        <f>COUNTA(Anggota!B5:B36)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F35)</f>
+        <f>COUNTA(Anggota!F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Nurjannah Abdullah, S.IP., M.A</t>
+          <t>Prof. Dr. Dwia Aries Tina Pulubuhu, MA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>International Development Cooperation</t>
+          <t>Conflict Resolution</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,7 +937,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57201469676</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Muh. Adnan Kasogi S, S.Sos., M.Si</t>
+          <t>Nurjannah Abdullah, S.IP., M.A</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Conflict Sociology &amp; Disaster Sociology</t>
+          <t>International Development Cooperation</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ishaq Rahman, , M.Si</t>
+          <t>Muh. Adnan Kasogi S, S.Sos., M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,24 +1006,16 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Paradiplomacy and Good Governance</t>
+          <t>Conflict Sociology &amp; Disaster Sociology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0321-4082</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>57223007361</t>
-        </is>
-      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1032,12 +1028,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ridwan, SS., MA</t>
+          <t>Ishaq Rahman, , M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1045,14 +1041,26 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Paradiplomacy and Good Governance</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0321-4082</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57223007361</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1065,12 +1073,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Marwan, S.I.P., M.Si.</t>
+          <t>Muhammad Ridwan, SS., MA</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1078,11 +1086,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Political Economy &amp; Global Politics</t>
-        </is>
-      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1102,22 +1106,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Elvita Bellani, S.Psi., M.Sc</t>
+          <t>Marwan, S.I.P., M.Si.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin Univesity</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Behavioral Economics</t>
+          <t>Political Economy &amp; Global Politics</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1126,11 +1130,7 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>57209396077</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1143,37 +1143,33 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Andi Ahmad Yani, S.Sos.,M.Si, MPA, M.Sc</t>
+          <t>Elvita Bellani, S.Psi., M.Sc</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Hasanuddin Univesity</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Post-conflict Governance</t>
+          <t>Behavioral Economics</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-3401-7639</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57204899767</t>
+          <t>57209396077</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1188,12 +1184,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Agussalim, S.I.P.,MIRAP</t>
+          <t>Andi Ahmad Yani, S.Sos.,M.Si, MPA, M.Sc</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1203,7 +1199,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Security Studies &amp; Religious Politics</t>
+          <t>Post-conflict Governance</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1212,13 +1208,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8697-7936</t>
+          <t>0000-0003-3401-7639</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57215376432</t>
+          <t>57204899767</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1233,12 +1229,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ichlas Nanang Afandi, S.Psi., MA</t>
+          <t>Agussalim, S.I.P.,MIRAP</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1248,7 +1244,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Social Psicology</t>
+          <t>Security Studies &amp; Religious Politics</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1257,13 +1253,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-1088-668X</t>
+          <t>0000-0001-8697-7936</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>58645024400</t>
+          <t>57215376432</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1278,12 +1274,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Amril, S.A.P., MPA</t>
+          <t>Dr. Ichlas Nanang Afandi, S.Psi., MA</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Disaster Governance</t>
+          <t>Social Psicology</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1302,13 +1298,13 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7610-3220</t>
+          <t>0009-0005-1088-668X</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>57212136118</t>
+          <t>58645024400</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1323,12 +1319,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ria Renita Abbas, S.Sos.,M.Si</t>
+          <t>Dr. Amril, S.A.P., MPA</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1338,16 +1334,24 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Rural and Agrarian Sociology</t>
+          <t>Disaster Governance</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7610-3220</t>
+        </is>
+      </c>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>57212136118</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1360,12 +1364,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Suharman Hamzah, ST., MT., Ph.D., HSE</t>
+          <t>Dr. Ria Renita Abbas, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1375,7 +1379,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Infrastructure Asset Management &amp; Human Security Engineering</t>
+          <t>Rural and Agrarian Sociology</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1384,11 +1388,7 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>57197842978</t>
-        </is>
-      </c>
+      <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1401,37 +1401,33 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Febriansyah</t>
+          <t>Prof. Ir. Suharman Hamzah, ST., MT., Ph.D., HSE</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>EXTERNAL COLLABORATORS</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Universiti Sains Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Comparative Politics</t>
+          <t>Infrastructure Asset Management &amp; Human Security Engineering</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-3368-0105</t>
-        </is>
-      </c>
+      <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>56146447300</t>
+          <t>57197842978</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1446,22 +1442,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sana Jaffrey</t>
+          <t>Dr. Muhammad Febriansyah</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>EXTERNAL COLLABORATORS</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Australian National University</t>
+          <t>Universiti Sains Malaysia</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Comparative Democratization, Collective Violence, and Bureaucracy</t>
+          <t>Comparative Politics</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1470,11 +1466,15 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1454-4968</t>
+          <t>0000-0003-3368-0105</t>
         </is>
       </c>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>56146447300</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1487,29 +1487,33 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Rifqy Tenribali Eshanasir, M.Sc</t>
+          <t>Dr. Sana Jaffrey</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>RESEARCHERS</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Australian National University</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>International Relations and Peace Studies</t>
+          <t>Comparative Democratization, Collective Violence, and Bureaucracy</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-1454-4968</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
@@ -1524,12 +1528,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Yunisa Syalom P, S.Sos, M.Sc</t>
+          <t>Rifqy Tenribali Eshanasir, M.Sc</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>RESEARCHERS</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1539,7 +1543,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Peace and Conflict Resolution</t>
+          <t>International Relations and Peace Studies</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1561,12 +1565,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Sulfadli, SAP, MAP</t>
+          <t>Yunisa Syalom P, S.Sos, M.Sc</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>RESEARCHERS</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1576,7 +1580,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Public Administration</t>
+          <t>Peace and Conflict Resolution</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1598,12 +1602,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Abd. Rasyid</t>
+          <t>Sulfadli, SAP, MAP</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>STUDENTS</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1613,7 +1617,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student in Sociology</t>
+          <t>Public Administration</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1635,12 +1639,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Mandi Tandi Pare</t>
+          <t>Abd. Rasyid</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>STUDENTS</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1670,10 +1674,26 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Mandi Tandi Pare</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Doctoral Student in Sociology</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Peace, Conflict, and Democracy Research Group (PCD-RG) is a collaborative effort among researchers, policy analysts, and practitioners committed to advancing the understanding of peacebuilding, conflict resolution, and democratic governance in diverse sociopolitical contexts. The initiative focuses on analyzing the root causes of conflict, exploring pathways to sustainable peace, and evaluating the role of democratic institutions in promoting social justice and stability. Through interdisciplinary collaboration and a shared commitment to addressing critical global challenges, the group aims to provide impactful insights that inform policy, empower communities, and contribute to inclusive, resilient, and democratic societies.</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
@@ -1681,7 +1701,11 @@
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1870,15 +1894,32 @@
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
